--- a/자문지/라이프자산운용_DB 목표전환형 랩 _4차_2026.5.18.xlsx
+++ b/자문지/라이프자산운용_DB 목표전환형 랩 _4차_2026.5.18.xlsx
@@ -4374,7 +4374,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="23" t="inlineStr">
         <is>
-          <t>DB금융투자 라이프 목표전환형 랩 현황</t>
+          <t>DB증권 라이프 목표전환형 랩 현황</t>
         </is>
       </c>
     </row>
